--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B230286-C15C-4832-979A-498627CB2A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9BAE50-3DA9-47C4-BC5F-97A013FDBA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF06CD2E-1996-44EE-8ECE-FA20E97B228D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC235A94-0B77-41CB-8BBA-54D44FE7A32C}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9BAE50-3DA9-47C4-BC5F-97A013FDBA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E264AB00-ECCC-4C49-AF5D-BB9EB05DE421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC235A94-0B77-41CB-8BBA-54D44FE7A32C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9488D9-8D5F-47C6-B8FC-414A4667ADCB}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E264AB00-ECCC-4C49-AF5D-BB9EB05DE421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040ED894-F568-44EA-AB18-DF7EF659F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9488D9-8D5F-47C6-B8FC-414A4667ADCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B06E4B-ED7F-4800-9F16-AD99F70EE138}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040ED894-F568-44EA-AB18-DF7EF659F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6112D361-086A-4FB0-94FA-2D2954F70E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B06E4B-ED7F-4800-9F16-AD99F70EE138}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEA56FB-89FA-443C-9FA0-347C4B0BCB12}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6112D361-086A-4FB0-94FA-2D2954F70E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329FE9EE-6979-4510-944B-90495256C37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEA56FB-89FA-443C-9FA0-347C4B0BCB12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6FE2BB8-AAB9-44E3-BEA7-9D7BD92C5EC1}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329FE9EE-6979-4510-944B-90495256C37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4797F5-4081-4D8C-B142-41B004476C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6FE2BB8-AAB9-44E3-BEA7-9D7BD92C5EC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC1544FB-F030-461A-ABC4-9B12B473A35D}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4797F5-4081-4D8C-B142-41B004476C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6552BD77-0BC8-408E-BE7F-C575787BAF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC1544FB-F030-461A-ABC4-9B12B473A35D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75D55E3-BB3E-4145-A19C-99B68665028A}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6552BD77-0BC8-408E-BE7F-C575787BAF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14565C67-0BE7-4C6D-9B09-4FC40E75FBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75D55E3-BB3E-4145-A19C-99B68665028A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C05E47E-09F8-48F7-9493-A22439BB2AE2}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14565C67-0BE7-4C6D-9B09-4FC40E75FBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B72E75E-9437-43BE-8DE4-881033EB637D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C05E47E-09F8-48F7-9493-A22439BB2AE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{960C8D04-9B6C-4331-A388-F2A9863DEA27}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
